--- a/astro-site/public/dl/manual-chef-ejecutivo/auditoria-interna-cocina.xlsx
+++ b/astro-site/public/dl/manual-chef-ejecutivo/auditoria-interna-cocina.xlsx
@@ -1875,7 +1875,7 @@
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>RD 486/1997, Anexo I, punto 3.1</t>
+          <t>RD 486/1997, Anexo I, punto 3, apartado 1.º</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
